--- a/www/download/COUNTRY.CZE.WIOD16.xlsx
+++ b/www/download/COUNTRY.CZE.WIOD16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>República Tcheca</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>38.4337479053607</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>38.0106733970899</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>32.5804002827979</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>28.1623503171081</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>25.6449710211827</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>23.9311739437378</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>22.5586977314974</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>20.2235511342379</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>16.949209997322</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>18.9405059766767</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>19.0539703710761</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>17.6613229390561</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>19.5577599324084</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>19.5630782112304</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>20.7195914096574</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>4.859</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4.846</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>4.877</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>4.838</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>4.829</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>4.923</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>4.989</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>5.093</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>5.204</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>5.11</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>5.057</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>5.043</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>5.065</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>5.081</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>5.109</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>4.155</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4.141</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>4.123</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>4.035</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>4.053</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>4.18</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>4.234</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>4.445</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>4.336</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>4.251</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>4.23</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>4.255</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>4.296</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>4.326</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>8809.001</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>8373.354</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>8393.93</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>8259.118</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>8336.588</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>8524.689</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>8567.291</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>8728.184</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>8932.223</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>8753.092</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>8772.629</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>8794.115</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>8770.942</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>8781.362</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>8846.175</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7503.32</t>
+          <t>11257617252.2575</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7128.206</t>
+          <t>11015142476.5008</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>7068.005</t>
+          <t>11227605350.3231</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>6859.997</t>
+          <t>11339072693.9233</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>6969.614</t>
+          <t>11538351608.2744</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>7215.308</t>
+          <t>11759270671.9504</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>7246.877</t>
+          <t>12190924927.7493</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>7395.33</t>
+          <t>12604386462.8351</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>7603.847</t>
+          <t>12901115397.9804</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>7406.866</t>
+          <t>11685990246.3948</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>7361.172</t>
+          <t>12093964222.0478</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>7360.311</t>
+          <t>13149229426.0377</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>7355.239</t>
+          <t>12334469277.7656</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>7406.026</t>
+          <t>12590472727.1993</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>7472.025</t>
+          <t>12638810416.3263</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>1639863937.94268</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1642610529.0481</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>1757409598.28783</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>1876057202.72793</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1927828796.16483</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2046672875.68442</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2030935400.07947</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2074465664.36433</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2154675816.6072</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>2003604558.47391</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1949133898.86183</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>2079507853.72554</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1977823120.92538</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2080239355.92722</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2022204552.69788</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>4232368.94325059</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3750562.84548617</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>3240378.670751</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2637452.17576088</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2199431.64061781</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1978015.85032299</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>1723398.47116678</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1451130.71113709</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>1204728.44655707</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1390003.40656484</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1378188.03314616</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1290455.71535258</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1344496.4196276</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1380942.84508523</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1368956.17943609</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>42381.057312552</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>39643.8688279002</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>39589.9756462459</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>42067.9442544613</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>47583.6759230206</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>52044.9158870251</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>54621.6852488517</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>62496.4542100022</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>68634.4150274227</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>59736.0975420007</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>66179.8971314147</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>71333.4319476936</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>69159.0522306562</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>68669.5762734488</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>69387.6473648566</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>91472.2623257613</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>88660.8124424059</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>90913.331488038</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>99922.9664740661</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>112414.290100837</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>123007.627942416</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>134719.667379593</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>157266.129488859</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>174715.167128248</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>144021.357084318</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>165129.073046567</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>190662.815083237</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>174261.392387179</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>177701.407917291</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>179209.981656313</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>3.57557473299489</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3.33955942321326</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>3.02183134022146</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>2.65660332212955</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2.61526605156286</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2.52538409323822</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2.5682459420996</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2.56493246768976</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2.52899816361851</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>2.69677038748684</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>2.77663741023562</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>2.53944852230957</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>2.71885580777247</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2.56017973551843</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2.69498970320848</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>25073.3873071619</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>26777.9569435507</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>31014.3964548787</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>38067.1063868582</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>43673.3475074377</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>48784.427850061</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>54304.9375703613</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>66165.7954925089</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>81920.0424372915</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>74007.8717972692</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>75343.3469081141</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>83446.7404347647</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>76532.0804784598</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>77758.4768430917</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>75602.5029978607</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>38.4337479053607</t>
+          <t>394.676227434843</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>38.0106733970899</t>
+          <t>396.636490286525</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>32.5804002827979</t>
+          <t>426.22261200902</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>28.1623503171081</t>
+          <t>464.937957142733</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>25.6449710211827</t>
+          <t>475.662988545282</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>23.9311739437378</t>
+          <t>489.597178130962</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>22.5586977314974</t>
+          <t>479.660518994422</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>20.2235511342379</t>
+          <t>479.109081251116</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>16.949209997322</t>
+          <t>484.742556587798</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>18.9405059766767</t>
+          <t>462.071002890569</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>19.0539703710761</t>
+          <t>458.463324009886</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>17.6613229390561</t>
+          <t>491.59082723243</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>19.5577599324084</t>
+          <t>464.785063725751</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>19.5630782112304</t>
+          <t>484.237182791823</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>20.7195914096574</t>
+          <t>467.442859087373</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>-403065717.729037</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>-219949761.330089</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>70744119.701357</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>301057308.84351</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>685764219.702484</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>899572286.873502</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>1163508234.48991</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>1323537986.4054</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>1618820383.79003</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>1381394720.55326</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>1224257375.28775</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>1593016873.95189</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>1316764314.79362</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>1578998416.95511</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>1695347728.93014</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>-396209971.459008</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-196787409.163774</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>201199929.768096</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>450270280.646209</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>946729142.087993</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>1290312960.25246</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>1612749550.03674</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>1690912860.92709</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>2012019043.49648</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>1826213853.13356</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>1844934056.42484</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>2243358864.31866</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>1954434036.40476</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>2198583699.37387</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>2405561652.2987</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>-6855746.2700285</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.323</t>
+          <t>-23162352.1663149</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.386</t>
+          <t>-130455810.066739</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-149212971.802699</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>-260964922.385509</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.591</t>
+          <t>-390740673.378956</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.658</t>
+          <t>-449241315.546834</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.797</t>
+          <t>-367374874.52169</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>1.014</t>
+          <t>-393198659.706448</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.912</t>
+          <t>-444819132.580299</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.907</t>
+          <t>-620676681.137095</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-650341990.366771</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0.894</t>
+          <t>-637669721.611141</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0.897</t>
+          <t>-619585282.418752</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.864</t>
+          <t>-710213923.368558</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>1805.87057396461</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>1721.22761901312</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>1714.19545888893</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>1700.09367867224</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>1719.64825447269</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>1726.01810387722</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>1711.54670048723</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>1707.99151931711</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.567</t>
+          <t>1710.65559202608</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.467</t>
+          <t>1708.1704004022</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.486</t>
+          <t>1731.44974067671</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.548</t>
+          <t>1739.96042702876</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.492</t>
+          <t>1728.46863360241</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.493</t>
+          <t>1723.97140535998</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.493</t>
+          <t>1727.19655116618</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>1812.7792221406</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>1727.747286332</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>1721.20687725753</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>1707.10302086102</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>1726.39115919445</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>1731.72065296164</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>1717.24298377912</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>1713.70693147464</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>1716.38517688671</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>1712.88683158427</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.188</t>
+          <t>1734.66045203289</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>1743.66704134355</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>1731.78949914998</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>1728.25393606308</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>1731.41060943835</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>27786.2361251875</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>31021.5317050104</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>35058.959764142</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>44496.0486928703</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>63982.5127098577</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>77662.1699874495</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>94127.9835373625</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>119228.197209327</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>142918.837729027</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>115774.295481564</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>130707.892213482</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>155485.526404928</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>149238.453814207</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>152000.140868781</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>161569.691185924</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2708126282.48102</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2718715967.49074</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2692107025.67291</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>2834360658.95005</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>3477032646.06792</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>3903342495.43269</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>4146440339.0331</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>4539247337.40275</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>4685579947.53494</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>4285245305.83455</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>4671435581.34255</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>5311995496.59556</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>5246964842.50691</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>5417693995.91163</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>5652829778.48717</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>28441.8675523529</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>31332.648044276</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>34811.5326908265</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>44290.3116809566</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>60588.9116208657</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>72524.3787024848</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>87618.5923075387</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>111072.194634525</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>131570.986932523</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>104880.229907377</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>120616.010625938</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>142574.543560858</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>134659.842748043</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>135260.279453731</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>142205.629391916</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>8809.001</t>
+          <t>2406356242.04353</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>8373.354</t>
+          <t>2548572786.40776</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>8393.93</t>
+          <t>2722897718.97256</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>8259.118</t>
+          <t>3104115784.1831</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>8336.588</t>
+          <t>3694496929.99206</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>8524.689</t>
+          <t>4155080049.8569</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>8567.291</t>
+          <t>4562885570.46425</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>8728.184</t>
+          <t>5065122553.67624</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>8932.223</t>
+          <t>5327447015.33303</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>8753.092</t>
+          <t>4606104480.78482</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>8772.629</t>
+          <t>5022918990.24741</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>8794.115</t>
+          <t>5845674962.15051</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>8770.942</t>
+          <t>5354738774.78329</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>8781.362</t>
+          <t>5600753637.54894</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>8846.175</t>
+          <t>5749169445.07808</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>7503.32</t>
+          <t>-655.631427165439</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>7128.206</t>
+          <t>-311.116339265583</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>7068.005</t>
+          <t>247.427073315521</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>6859.997</t>
+          <t>205.737011913687</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>6969.614</t>
+          <t>3393.60108899201</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>7215.308</t>
+          <t>5137.79128496477</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>7246.877</t>
+          <t>6509.39122982384</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>7395.33</t>
+          <t>8156.00257480217</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>7603.847</t>
+          <t>11347.8507965036</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>7406.866</t>
+          <t>10894.0655741869</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>7361.172</t>
+          <t>10091.8815875436</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>7360.311</t>
+          <t>12910.9828440699</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>7355.239</t>
+          <t>14578.6110661639</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>7406.026</t>
+          <t>16739.8614150499</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>7472.025</t>
+          <t>19364.0617940078</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>11257.758</t>
+          <t>301770040.437487</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>11015.456</t>
+          <t>170143181.082981</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>11229.144</t>
+          <t>-30790693.2996514</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>11340.269</t>
+          <t>-269755125.233057</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>11538.251</t>
+          <t>-217464283.924143</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>11759.565</t>
+          <t>-251737554.424206</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>12191.006</t>
+          <t>-416445231.431151</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>12607.212</t>
+          <t>-525875216.273491</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>12903.225</t>
+          <t>-641867067.798091</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>11690.224</t>
+          <t>-320859174.950267</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>12088.646</t>
+          <t>-351483408.904865</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>13152.564</t>
+          <t>-533679465.554953</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>12328.74</t>
+          <t>-107773932.276383</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>12595.95</t>
+          <t>-183059641.637314</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>12626.779</t>
+          <t>-96339666.590915</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>29576.3765428</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>32703.182788</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>39038.0716308</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>46760.834418</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>57020.965194</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>64599.1293045</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>74386.8737448</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>89679.0078044</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>110499.0144258</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>94431.8489803</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>94553.52165</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>105214.9381115</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>95392.2129348</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>95631.7804284</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>97338.1646445</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>5215.895</t>
+          <t>0.0126012854839749</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>4925.32</t>
+          <t>0.0152471743757317</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>4889.279</t>
+          <t>0.0164833488812945</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>4773.792</t>
+          <t>0.0138762652136185</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>4884.052</t>
+          <t>0.0171892065383419</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>4975.385</t>
+          <t>0.0196653110020492</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>4942.774</t>
+          <t>0.0237635619407321</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>5008.895</t>
+          <t>0.023870394695635</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>5068.023</t>
+          <t>0.0231841505845144</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>4847.027</t>
+          <t>0.0198486894841376</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>4846.98</t>
+          <t>0.0172642227252973</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>4919.573</t>
+          <t>0.0153267525885706</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>4895.176</t>
+          <t>0.0118454998244782</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>4865.366</t>
+          <t>0.0113744022599726</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>4893.574</t>
+          <t>0.0174881916584861</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>23812.2236284</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>26004.406438</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>32564.7625809</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>39719.6607316</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>47276.559564</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>54288.8954405</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>61795.8543792</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>74826.3245142</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>95393.7676302</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>82815.1582609</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>83397.42159</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>92051.0318287</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>85054.1169208</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>85596.2943009</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>82643.038955</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1639.897</t>
+          <t>27505.070351272</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1642.68</t>
+          <t>29963.52993018</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1757.676</t>
+          <t>37860.689840919</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>1876.254</t>
+          <t>46713.171137596</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>1927.784</t>
+          <t>55337.56730814</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>2046.723</t>
+          <t>62839.47973198</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2030.977</t>
+          <t>71532.985157512</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2074.855</t>
+          <t>86554.098159179</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2154.922</t>
+          <t>109750.381303548</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2004.088</t>
+          <t>95479.045397567</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1948.724</t>
+          <t>97034.5751564</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>2079.913</t>
+          <t>107288.836546311</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>1976.967</t>
+          <t>98898.347084978</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>2080.777</t>
+          <t>98911.850635509</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2020.977</t>
+          <t>95366.102107545</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>357.55</t>
+          <t>303872.26426</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>333.94</t>
+          <t>322838.6372376</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>302.12</t>
+          <t>385912.4163873</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>265.62</t>
+          <t>460142.0284204</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>261.53</t>
+          <t>530229.337704</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>252.53</t>
+          <t>591082.8709555</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>256.82</t>
+          <t>657880.4847976</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>256.43</t>
+          <t>797369.358772</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>252.86</t>
+          <t>1013990.6817318</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>269.59</t>
+          <t>912380.1138829</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>277.74</t>
+          <t>907078.0873175</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>253.88</t>
+          <t>990068.4144862</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>272.05</t>
+          <t>893574.9319144</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>255.93</t>
+          <t>896508.4538655</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>269.72</t>
+          <t>863711.6749155</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4.232</t>
+          <t>35630.4488354732</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3.751</t>
+          <t>36267.2359263789</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>3.241</t>
+          <t>37970.5887841003</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2.638</t>
+          <t>39552.1848481384</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>41057.7278467106</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1.978</t>
+          <t>42931.7337704416</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.723</t>
+          <t>45072.8131426085</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.451</t>
+          <t>46916.3911540872</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>48939.3927146812</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.391</t>
+          <t>46352.156442265</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1.378</t>
+          <t>48106.001125696</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1.291</t>
+          <t>49333.3486010795</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1.344</t>
+          <t>49742.0418080212</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>1.381</t>
+          <t>49240.6877922559</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>1.368</t>
+          <t>48857.6886359964</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>31057.3463985819</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>31593.8844486885</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>32720.7967194919</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>33649.8204156789</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>34995.3616518899</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>36934.6242279016</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>38827.4030139661</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>40436.042503048</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>42535.5146769981</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>40162.3299418973</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>41345.2261776</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>42396.8466159451</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>42790.1570758402</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>42592.3055565262</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>42231.3842543353</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>28902.568459764</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>31700.333940736</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>37375.525451814</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>44452.159209152</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>52787.56910592</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>60408.256335385</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>69938.521220448</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>85199.316804602</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>105428.555093856</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>92117.421369233</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>91003.3450368</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>98621.274069353</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>87116.92217761</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>87955.724626824</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>90707.258306455</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>7503320000</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>7128206000</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>7068005000</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>6859997000</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>6969614000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>7215308000</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>7246877000</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>7395330000</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>7603847000</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>7406866000</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>7361172000</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>7360311000</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>7355239000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>7406026000</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>7472025000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>8809001224.2778</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>8373354448.47941</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>8393930062.8032</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>8259118054.19751</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>8336587532.54569</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>8524689306.71469</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>8567290901.21437</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>8728183595.10938</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>8932222935.18434</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>8753091513.55203</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>8772628917.64785</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>8794114976.33455</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>8770942322.6599</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>8781361944.37269</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>8846175028.06073</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>5215895068.51339</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>4925319895.33369</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>4889278779.13523</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>4773792200.30514</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>4884051512.68133</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>4975384561.5243</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>4942773963.50499</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>5008894566.04545</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>5068023132.13998</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>4847027325.43213</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>4846979961.55058</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>4919573132.37706</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>4895176110.62757</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>4865366219.61712</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>4893574075.36141</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>4859390</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4846400</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>4876770</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>4838090</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>4828910</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>4922670</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>4988980</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>5093160</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>5204090</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>5110140</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>5057260</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>5043460</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>5064670</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>5081060</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>5109230</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>4154960</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4141350</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>4123220</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>4035070</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>4052930</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>4180320</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>4234110</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>4329840</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>4444990</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>4336140</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>4251450</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>4230160</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>4255350</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>4295910</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>4326100</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>8809001224.2778</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>8373354448.47941</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>8393930062.8032</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>8259118054.19751</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>8336587532.54569</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>8524689306.71469</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>8567290901.21437</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>8728183595.10938</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>8932222935.18434</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>8753091513.55203</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>8772628917.64785</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>8794114976.33455</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>8770942322.6599</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>8781361944.37269</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>8846175028.06073</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>7503320000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>7128206000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>7068005000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>6859997000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>6969614000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>7215308000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>7246877000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>7395330000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>7603847000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>7406866000</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>7361172000</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>7360311000</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>7355239000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>7406026000</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>7472025000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>137783.3099452</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>151346.0164176</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>182446.193061</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>227352.7929276</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>274328.951052</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>312337.707192</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>370516.8223576</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>456066.7381697</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>566629.3002162</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>467214.9208103</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>485891.697095</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>548193.7583843</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>491599.3975398</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>492524.4328098</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>492771.782905</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>56407.6395916</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>61663.864134</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>75236.2149858</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>91165.331412</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>108125.136804</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>123247.7356495</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>141471.5085944</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>171753.4164472</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>215178.9375774</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>187596.4667668</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>188037.9222925</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>205910.1128805</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>186015.2702852</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>186867.5757735</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>186073.360414</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>410947.437317005</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>416255.360298232</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>412712.874200826</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>413769.953693106</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>416129.737277957</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>419298.68164638</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>425236.226235358</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>445722.636057738</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>456707.275649841</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>450228.100568903</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>449694.3426532</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>449640.768363888</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>446694.290502901</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>449457.951528099</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>454006.786561931</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD16</t>
